--- a/grupos/2AEM - Estadisticos 20232.xlsx
+++ b/grupos/2AEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="94">
   <si>
     <t>Materia</t>
   </si>
@@ -182,18 +182,18 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Flores Paz Victor</t>
   </si>
   <si>
@@ -215,6 +215,9 @@
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -239,10 +242,13 @@
     <t>JIMENEZ</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
+    <t>ZEPAHUA</t>
   </si>
   <si>
     <t>ATLAHUA</t>
@@ -254,18 +260,21 @@
     <t>MARCELINO</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
     <t>JUAN SEBASTIAN</t>
   </si>
   <si>
+    <t>JOEL MIGUEL</t>
+  </si>
+  <si>
     <t>ERICK ANGEL</t>
   </si>
   <si>
@@ -291,9 +300,6 @@
   </si>
   <si>
     <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOEL MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -858,31 +864,31 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -971,31 +977,31 @@
         <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -1025,16 +1031,16 @@
         <v>-1</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG5">
         <v>7</v>
@@ -1084,31 +1090,31 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1153,13 +1159,13 @@
         <v>8</v>
       </c>
       <c r="AH6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI6">
         <v>10</v>
       </c>
       <c r="AJ6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK6">
         <v>-1</v>
@@ -1197,31 +1203,31 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1254,19 +1260,19 @@
         <v>9</v>
       </c>
       <c r="AD7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG7">
         <v>8</v>
       </c>
       <c r="AH7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI7">
         <v>10</v>
@@ -1310,31 +1316,31 @@
         <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1379,13 +1385,13 @@
         <v>5</v>
       </c>
       <c r="AH8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI8">
         <v>6</v>
       </c>
       <c r="AJ8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK8">
         <v>-1</v>
@@ -1423,31 +1429,31 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1486,19 +1492,19 @@
         <v>5</v>
       </c>
       <c r="AF9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG9">
         <v>7</v>
       </c>
       <c r="AH9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK9">
         <v>-1</v>
@@ -1536,31 +1542,31 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1596,7 +1602,7 @@
         <v>6</v>
       </c>
       <c r="AE10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF10">
         <v>9</v>
@@ -1605,13 +1611,13 @@
         <v>6</v>
       </c>
       <c r="AH10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK10">
         <v>-1</v>
@@ -1649,31 +1655,31 @@
         <v>10</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1762,31 +1768,31 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1816,7 +1822,7 @@
         <v>-1</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD12">
         <v>8</v>
@@ -1875,31 +1881,31 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1932,7 +1938,7 @@
         <v>9</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE13">
         <v>9</v>
@@ -1944,13 +1950,13 @@
         <v>9</v>
       </c>
       <c r="AH13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI13">
         <v>10</v>
       </c>
       <c r="AJ13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK13">
         <v>-1</v>
@@ -1988,31 +1994,31 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -2048,7 +2054,7 @@
         <v>8</v>
       </c>
       <c r="AE14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF14">
         <v>8</v>
@@ -2057,7 +2063,7 @@
         <v>9</v>
       </c>
       <c r="AH14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI14">
         <v>10</v>
@@ -2101,31 +2107,31 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -2164,19 +2170,19 @@
         <v>8</v>
       </c>
       <c r="AF15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG15">
         <v>8</v>
       </c>
       <c r="AH15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK15">
         <v>-1</v>
@@ -2214,31 +2220,31 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -2274,7 +2280,7 @@
         <v>5</v>
       </c>
       <c r="AE16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF16">
         <v>5</v>
@@ -2286,10 +2292,10 @@
         <v>5</v>
       </c>
       <c r="AI16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK16">
         <v>-1</v>
@@ -2327,31 +2333,31 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2387,10 +2393,10 @@
         <v>5</v>
       </c>
       <c r="AE17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG17">
         <v>6</v>
@@ -2399,10 +2405,10 @@
         <v>5</v>
       </c>
       <c r="AI17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK17">
         <v>-1</v>
@@ -2440,31 +2446,31 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2500,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="AE18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF18">
         <v>5</v>
@@ -2553,31 +2559,31 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2616,7 +2622,7 @@
         <v>5</v>
       </c>
       <c r="AF19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG19">
         <v>7</v>
@@ -2628,7 +2634,7 @@
         <v>6</v>
       </c>
       <c r="AJ19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK19">
         <v>-1</v>
@@ -2666,31 +2672,31 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2729,19 +2735,19 @@
         <v>5</v>
       </c>
       <c r="AF20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG20">
         <v>6</v>
       </c>
       <c r="AH20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI20">
         <v>6</v>
       </c>
       <c r="AJ20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK20">
         <v>-1</v>
@@ -2779,31 +2785,31 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2848,13 +2854,13 @@
         <v>5</v>
       </c>
       <c r="AH21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK21">
         <v>-1</v>
@@ -2892,31 +2898,31 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2961,13 +2967,13 @@
         <v>7</v>
       </c>
       <c r="AH22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AJ22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK22">
         <v>-1</v>
@@ -3005,31 +3011,31 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -3062,19 +3068,19 @@
         <v>7</v>
       </c>
       <c r="AD23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG23">
         <v>10</v>
       </c>
       <c r="AH23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI23">
         <v>10</v>
@@ -3118,31 +3124,31 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -3172,25 +3178,25 @@
         <v>-1</v>
       </c>
       <c r="AC24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD24">
         <v>7</v>
       </c>
       <c r="AE24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG24">
         <v>9</v>
       </c>
       <c r="AH24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ24">
         <v>9</v>
@@ -3231,31 +3237,31 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -3294,7 +3300,7 @@
         <v>5</v>
       </c>
       <c r="AF25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG25">
         <v>5</v>
@@ -3306,7 +3312,7 @@
         <v>6</v>
       </c>
       <c r="AJ25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK25">
         <v>-1</v>
@@ -3344,31 +3350,31 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -3407,19 +3413,19 @@
         <v>5</v>
       </c>
       <c r="AF26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG26">
         <v>5</v>
       </c>
       <c r="AH26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK26">
         <v>-1</v>
@@ -3457,31 +3463,31 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -3511,16 +3517,16 @@
         <v>-1</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE27">
         <v>7</v>
       </c>
       <c r="AF27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG27">
         <v>9</v>
@@ -3529,10 +3535,10 @@
         <v>9</v>
       </c>
       <c r="AI27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK27">
         <v>-1</v>
@@ -3570,31 +3576,31 @@
         <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -3633,7 +3639,7 @@
         <v>7</v>
       </c>
       <c r="AF28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG28">
         <v>6</v>
@@ -3645,7 +3651,7 @@
         <v>6</v>
       </c>
       <c r="AJ28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK28">
         <v>-1</v>
@@ -3829,25 +3835,25 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L4">
-        <v>84.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M4">
         <v>100</v>
       </c>
       <c r="N4">
-        <v>3.3</v>
+        <v>31.7</v>
       </c>
       <c r="O4">
         <v>73.3</v>
       </c>
       <c r="P4">
-        <v>68.8</v>
+        <v>46.9</v>
       </c>
       <c r="Q4">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3856,25 +3862,25 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U4">
-        <v>84.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="V4">
         <v>100</v>
       </c>
       <c r="W4">
-        <v>3.3</v>
+        <v>31.7</v>
       </c>
       <c r="X4">
         <v>73.3</v>
       </c>
       <c r="Y4">
-        <v>68.8</v>
+        <v>46.9</v>
       </c>
       <c r="Z4">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="AA4">
         <v>100</v>
@@ -3915,7 +3921,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -3930,10 +3936,10 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -3942,7 +3948,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -3957,10 +3963,10 @@
         <v>100</v>
       </c>
       <c r="Y5">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z5">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA5">
         <v>100</v>
@@ -4001,7 +4007,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -4010,16 +4016,16 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O6">
         <v>100</v>
       </c>
       <c r="P6">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -4028,7 +4034,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -4037,16 +4043,16 @@
         <v>100</v>
       </c>
       <c r="W6">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="X6">
         <v>100</v>
       </c>
       <c r="Y6">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z6">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA6">
         <v>100</v>
@@ -4102,10 +4108,10 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4129,10 +4135,10 @@
         <v>100</v>
       </c>
       <c r="Y7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z7">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="AA7">
         <v>100</v>
@@ -4173,25 +4179,25 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="L8">
-        <v>89.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O8">
         <v>53.3</v>
       </c>
       <c r="P8">
-        <v>43.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q8">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -4200,25 +4206,25 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U8">
-        <v>89.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V8">
         <v>100</v>
       </c>
       <c r="W8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X8">
         <v>53.3</v>
       </c>
       <c r="Y8">
-        <v>43.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Z8">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="AA8">
         <v>100</v>
@@ -4259,55 +4265,55 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>83.3</v>
+        <v>63.6</v>
       </c>
       <c r="L9">
-        <v>89.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M9">
         <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O9">
         <v>86.7</v>
       </c>
       <c r="P9">
-        <v>68.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="S9">
         <v>100</v>
       </c>
       <c r="T9">
-        <v>83.3</v>
+        <v>63.6</v>
       </c>
       <c r="U9">
-        <v>89.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V9">
         <v>100</v>
       </c>
       <c r="W9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="X9">
         <v>86.7</v>
       </c>
       <c r="Y9">
-        <v>68.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Z9">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA9">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="AB9">
         <v>100</v>
@@ -4345,25 +4351,25 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="L10">
-        <v>94.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M10">
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O10">
         <v>93.3</v>
       </c>
       <c r="P10">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -4372,25 +4378,25 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="U10">
-        <v>94.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V10">
         <v>100</v>
       </c>
       <c r="W10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X10">
         <v>93.3</v>
       </c>
       <c r="Y10">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Z10">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA10">
         <v>100</v>
@@ -4431,7 +4437,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -4440,7 +4446,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -4449,7 +4455,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -4458,7 +4464,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -4467,7 +4473,7 @@
         <v>100</v>
       </c>
       <c r="W11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X11">
         <v>100</v>
@@ -4476,7 +4482,7 @@
         <v>100</v>
       </c>
       <c r="Z11">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA11">
         <v>100</v>
@@ -4517,7 +4523,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -4526,7 +4532,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -4535,7 +4541,7 @@
         <v>93.8</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -4544,7 +4550,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4553,7 +4559,7 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="X12">
         <v>100</v>
@@ -4562,7 +4568,7 @@
         <v>93.8</v>
       </c>
       <c r="Z12">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA12">
         <v>100</v>
@@ -4603,25 +4609,25 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L13">
-        <v>89.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M13">
         <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O13">
         <v>93.3</v>
       </c>
       <c r="P13">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -4630,25 +4636,25 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U13">
-        <v>89.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V13">
         <v>100</v>
       </c>
       <c r="W13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X13">
         <v>93.3</v>
       </c>
       <c r="Y13">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z13">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA13">
         <v>100</v>
@@ -4689,25 +4695,25 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M14">
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O14">
         <v>93.3</v>
       </c>
       <c r="P14">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4716,25 +4722,25 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U14">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X14">
         <v>93.3</v>
       </c>
       <c r="Y14">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z14">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA14">
         <v>100</v>
@@ -4775,16 +4781,16 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L15">
-        <v>89.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M15">
         <v>100</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -4793,7 +4799,7 @@
         <v>93.8</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -4802,16 +4808,16 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U15">
-        <v>89.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="W15">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="X15">
         <v>100</v>
@@ -4820,7 +4826,7 @@
         <v>93.8</v>
       </c>
       <c r="Z15">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA15">
         <v>100</v>
@@ -4861,22 +4867,22 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="L16">
-        <v>94.7</v>
+        <v>92.7</v>
       </c>
       <c r="M16">
         <v>100</v>
       </c>
       <c r="N16">
-        <v>6.7</v>
+        <v>28.3</v>
       </c>
       <c r="O16">
         <v>86.7</v>
       </c>
       <c r="P16">
-        <v>81.3</v>
+        <v>56.3</v>
       </c>
       <c r="Q16">
         <v>100</v>
@@ -4888,22 +4894,22 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="U16">
-        <v>94.7</v>
+        <v>92.7</v>
       </c>
       <c r="V16">
         <v>100</v>
       </c>
       <c r="W16">
-        <v>6.7</v>
+        <v>28.3</v>
       </c>
       <c r="X16">
         <v>86.7</v>
       </c>
       <c r="Y16">
-        <v>81.3</v>
+        <v>56.3</v>
       </c>
       <c r="Z16">
         <v>100</v>
@@ -4947,16 +4953,16 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="L17">
-        <v>84.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M17">
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="O17">
         <v>86.7</v>
@@ -4965,7 +4971,7 @@
         <v>75</v>
       </c>
       <c r="Q17">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4974,16 +4980,16 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>66.7</v>
+        <v>72.7</v>
       </c>
       <c r="U17">
-        <v>84.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="V17">
         <v>100</v>
       </c>
       <c r="W17">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="X17">
         <v>86.7</v>
@@ -4992,7 +4998,7 @@
         <v>75</v>
       </c>
       <c r="Z17">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="AA17">
         <v>100</v>
@@ -5033,58 +5039,58 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>58.3</v>
+        <v>31.8</v>
       </c>
       <c r="L18">
-        <v>84.2</v>
+        <v>39</v>
       </c>
       <c r="M18">
         <v>100</v>
       </c>
       <c r="N18">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="O18">
         <v>66.7</v>
       </c>
       <c r="P18">
-        <v>68.8</v>
+        <v>37.5</v>
       </c>
       <c r="Q18">
-        <v>91.7</v>
+        <v>74</v>
       </c>
       <c r="R18">
-        <v>71.2</v>
+        <v>43.8</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>48.6</v>
       </c>
       <c r="T18">
-        <v>58.3</v>
+        <v>31.8</v>
       </c>
       <c r="U18">
-        <v>84.2</v>
+        <v>39</v>
       </c>
       <c r="V18">
         <v>100</v>
       </c>
       <c r="W18">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
       <c r="X18">
         <v>66.7</v>
       </c>
       <c r="Y18">
-        <v>68.8</v>
+        <v>37.5</v>
       </c>
       <c r="Z18">
-        <v>91.7</v>
+        <v>74</v>
       </c>
       <c r="AA18">
-        <v>71.2</v>
+        <v>43.8</v>
       </c>
       <c r="AB18">
-        <v>100</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="19" spans="1:28">
@@ -5119,55 +5125,55 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M19">
         <v>100</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O19">
         <v>93.3</v>
       </c>
       <c r="P19">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q19">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="R19">
-        <v>95.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="U19">
-        <v>100</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V19">
         <v>100</v>
       </c>
       <c r="W19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X19">
         <v>93.3</v>
       </c>
       <c r="Y19">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Z19">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="AA19">
-        <v>95.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AB19">
         <v>100</v>
@@ -5205,16 +5211,16 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L20">
-        <v>84.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O20">
         <v>93.3</v>
@@ -5223,25 +5229,25 @@
         <v>87.5</v>
       </c>
       <c r="Q20">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="R20">
-        <v>68.5</v>
+        <v>84</v>
       </c>
       <c r="S20">
         <v>100</v>
       </c>
       <c r="T20">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U20">
-        <v>84.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="V20">
         <v>100</v>
       </c>
       <c r="W20">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X20">
         <v>93.3</v>
@@ -5250,10 +5256,10 @@
         <v>87.5</v>
       </c>
       <c r="Z20">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="AA20">
-        <v>68.5</v>
+        <v>84</v>
       </c>
       <c r="AB20">
         <v>100</v>
@@ -5291,55 +5297,55 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>58.3</v>
+        <v>72.7</v>
       </c>
       <c r="L21">
-        <v>84.2</v>
+        <v>92.7</v>
       </c>
       <c r="M21">
         <v>100</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O21">
         <v>46.7</v>
       </c>
       <c r="P21">
-        <v>50</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Q21">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="R21">
-        <v>95.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="S21">
         <v>100</v>
       </c>
       <c r="T21">
-        <v>58.3</v>
+        <v>72.7</v>
       </c>
       <c r="U21">
-        <v>84.2</v>
+        <v>92.7</v>
       </c>
       <c r="V21">
         <v>100</v>
       </c>
       <c r="W21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X21">
         <v>46.7</v>
       </c>
       <c r="Y21">
-        <v>50</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z21">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="AA21">
-        <v>95.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AB21">
         <v>100</v>
@@ -5377,7 +5383,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>75</v>
+        <v>81.8</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -5386,7 +5392,7 @@
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O22">
         <v>93.3</v>
@@ -5395,16 +5401,16 @@
         <v>81.3</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="S22">
         <v>100</v>
       </c>
       <c r="T22">
-        <v>75</v>
+        <v>81.8</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -5413,7 +5419,7 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X22">
         <v>93.3</v>
@@ -5422,10 +5428,10 @@
         <v>81.3</v>
       </c>
       <c r="Z22">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="AA22">
-        <v>100</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AB22">
         <v>100</v>
@@ -5478,10 +5484,10 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -5505,10 +5511,10 @@
         <v>100</v>
       </c>
       <c r="Y23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z23">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA23">
         <v>100</v>
@@ -5549,7 +5555,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -5564,10 +5570,10 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5576,7 +5582,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -5591,10 +5597,10 @@
         <v>100</v>
       </c>
       <c r="Y24">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z24">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA24">
         <v>100</v>
@@ -5635,25 +5641,25 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>83.3</v>
+        <v>77.3</v>
       </c>
       <c r="L25">
-        <v>94.7</v>
+        <v>92.7</v>
       </c>
       <c r="M25">
         <v>100</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q25">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -5662,25 +5668,25 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>83.3</v>
+        <v>77.3</v>
       </c>
       <c r="U25">
-        <v>94.7</v>
+        <v>92.7</v>
       </c>
       <c r="V25">
         <v>100</v>
       </c>
       <c r="W25">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="X25">
         <v>100</v>
       </c>
       <c r="Y25">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="Z25">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="AA25">
         <v>100</v>
@@ -5721,25 +5727,25 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="L26">
-        <v>89.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O26">
         <v>53.3</v>
       </c>
       <c r="P26">
-        <v>50</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Q26">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -5748,25 +5754,25 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>36.4</v>
       </c>
       <c r="U26">
-        <v>89.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="V26">
         <v>100</v>
       </c>
       <c r="W26">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X26">
         <v>53.3</v>
       </c>
       <c r="Y26">
-        <v>50</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Z26">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="AA26">
         <v>100</v>
@@ -5807,10 +5813,10 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L27">
-        <v>94.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -5822,10 +5828,10 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -5834,10 +5840,10 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U27">
-        <v>94.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5849,10 +5855,10 @@
         <v>100</v>
       </c>
       <c r="Y27">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z27">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="AA27">
         <v>100</v>
@@ -5896,22 +5902,22 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>94.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M28">
         <v>100</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O28">
         <v>100</v>
       </c>
       <c r="P28">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q28">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -5923,22 +5929,22 @@
         <v>100</v>
       </c>
       <c r="U28">
-        <v>94.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="V28">
         <v>100</v>
       </c>
       <c r="W28">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="X28">
         <v>100</v>
       </c>
       <c r="Y28">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z28">
-        <v>95.8</v>
+        <v>86</v>
       </c>
       <c r="AA28">
         <v>100</v>
@@ -6051,7 +6057,7 @@
         <v>60</v>
       </c>
       <c r="H3">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6062,7 +6068,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -6071,19 +6077,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G4" s="2">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6115,7 +6121,7 @@
         <v>44</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6126,7 +6132,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -6135,19 +6141,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G6" s="2">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H6">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6158,7 +6164,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -6179,7 +6185,7 @@
         <v>28</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6199,19 +6205,19 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G8" s="2">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="H8">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6231,19 +6237,19 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G9" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H9">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6275,7 +6281,7 @@
         <v>4</v>
       </c>
       <c r="H10">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -6325,7 +6331,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6363,10 +6369,10 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6386,10 +6392,10 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -6403,39 +6409,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920003</v>
+        <v>23330051920024</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920002</v>
+        <v>23330051920024</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -6449,16 +6455,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920004</v>
+        <v>23330051920003</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -6472,16 +6478,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920009</v>
+        <v>23330051920002</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -6495,16 +6501,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920026</v>
+        <v>23330051920004</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
         <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
@@ -6518,16 +6524,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920010</v>
+        <v>23330051920009</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -6541,16 +6547,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920012</v>
+        <v>23330051920026</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -6564,16 +6570,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920013</v>
+        <v>23330051920010</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -6587,16 +6593,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920020</v>
+        <v>23330051920012</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
@@ -6610,16 +6616,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920024</v>
+        <v>23330051920013</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
@@ -6628,6 +6634,52 @@
         <v>52</v>
       </c>
       <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920021</v>
+      </c>
+      <c r="B14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920020</v>
+      </c>
+      <c r="B15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2AEM - Estadisticos 20232.xlsx
+++ b/grupos/2AEM - Estadisticos 20232.xlsx
@@ -876,7 +876,7 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>5</v>
@@ -989,7 +989,7 @@
         <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -1102,7 +1102,7 @@
         <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>7</v>
@@ -1215,7 +1215,7 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>10</v>
@@ -1328,7 +1328,7 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>7</v>
@@ -1441,7 +1441,7 @@
         <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>9</v>
@@ -1554,7 +1554,7 @@
         <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>8</v>
@@ -1608,7 +1608,7 @@
         <v>9</v>
       </c>
       <c r="AG10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH10">
         <v>7</v>
@@ -1667,7 +1667,7 @@
         <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>10</v>
@@ -1780,7 +1780,7 @@
         <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>10</v>
@@ -1834,7 +1834,7 @@
         <v>10</v>
       </c>
       <c r="AG12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH12">
         <v>10</v>
@@ -1893,7 +1893,7 @@
         <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>10</v>
@@ -2006,7 +2006,7 @@
         <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>10</v>
@@ -2119,7 +2119,7 @@
         <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>10</v>
@@ -2232,7 +2232,7 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
         <v>5</v>
@@ -2345,7 +2345,7 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>5</v>
@@ -2399,7 +2399,7 @@
         <v>5</v>
       </c>
       <c r="AG17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH17">
         <v>5</v>
@@ -2458,7 +2458,7 @@
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -2571,7 +2571,7 @@
         <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>5</v>
@@ -2684,7 +2684,7 @@
         <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>7</v>
@@ -2797,7 +2797,7 @@
         <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>9</v>
@@ -2910,7 +2910,7 @@
         <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>7</v>
@@ -3023,7 +3023,7 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
         <v>10</v>
@@ -3136,7 +3136,7 @@
         <v>9</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
         <v>10</v>
@@ -3190,7 +3190,7 @@
         <v>8</v>
       </c>
       <c r="AG24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH24">
         <v>9</v>
@@ -3249,7 +3249,7 @@
         <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
         <v>5</v>
@@ -3362,7 +3362,7 @@
         <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>7</v>
@@ -3475,7 +3475,7 @@
         <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
         <v>8</v>
@@ -3529,7 +3529,7 @@
         <v>9</v>
       </c>
       <c r="AG27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH27">
         <v>9</v>
@@ -3588,7 +3588,7 @@
         <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>5</v>
@@ -3847,7 +3847,7 @@
         <v>31.7</v>
       </c>
       <c r="O4">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="P4">
         <v>46.9</v>
@@ -3874,7 +3874,7 @@
         <v>31.7</v>
       </c>
       <c r="X4">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="Y4">
         <v>46.9</v>
@@ -4019,7 +4019,7 @@
         <v>98.3</v>
       </c>
       <c r="O6">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="P6">
         <v>90.59999999999999</v>
@@ -4046,7 +4046,7 @@
         <v>98.3</v>
       </c>
       <c r="X6">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Y6">
         <v>90.59999999999999</v>
@@ -4191,7 +4191,7 @@
         <v>95</v>
       </c>
       <c r="O8">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
       <c r="P8">
         <v>65.59999999999999</v>
@@ -4218,7 +4218,7 @@
         <v>95</v>
       </c>
       <c r="X8">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
       <c r="Y8">
         <v>65.59999999999999</v>
@@ -4277,7 +4277,7 @@
         <v>90</v>
       </c>
       <c r="O9">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="P9">
         <v>78.09999999999999</v>
@@ -4304,7 +4304,7 @@
         <v>90</v>
       </c>
       <c r="X9">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="Y9">
         <v>78.09999999999999</v>
@@ -4621,7 +4621,7 @@
         <v>95</v>
       </c>
       <c r="O13">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="P13">
         <v>90.59999999999999</v>
@@ -4648,7 +4648,7 @@
         <v>95</v>
       </c>
       <c r="X13">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="Y13">
         <v>90.59999999999999</v>
@@ -4707,7 +4707,7 @@
         <v>95</v>
       </c>
       <c r="O14">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="P14">
         <v>90.59999999999999</v>
@@ -4734,7 +4734,7 @@
         <v>95</v>
       </c>
       <c r="X14">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="Y14">
         <v>90.59999999999999</v>
@@ -5051,7 +5051,7 @@
         <v>3.3</v>
       </c>
       <c r="O18">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="P18">
         <v>37.5</v>
@@ -5078,7 +5078,7 @@
         <v>3.3</v>
       </c>
       <c r="X18">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="Y18">
         <v>37.5</v>
@@ -5137,7 +5137,7 @@
         <v>95</v>
       </c>
       <c r="O19">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="P19">
         <v>81.3</v>
@@ -5164,7 +5164,7 @@
         <v>95</v>
       </c>
       <c r="X19">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="Y19">
         <v>81.3</v>
@@ -5223,7 +5223,7 @@
         <v>93.3</v>
       </c>
       <c r="O20">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="P20">
         <v>87.5</v>
@@ -5250,7 +5250,7 @@
         <v>93.3</v>
       </c>
       <c r="X20">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="Y20">
         <v>87.5</v>
@@ -5309,7 +5309,7 @@
         <v>95</v>
       </c>
       <c r="O21">
-        <v>46.7</v>
+        <v>70</v>
       </c>
       <c r="P21">
         <v>71.90000000000001</v>
@@ -5336,7 +5336,7 @@
         <v>95</v>
       </c>
       <c r="X21">
-        <v>46.7</v>
+        <v>70</v>
       </c>
       <c r="Y21">
         <v>71.90000000000001</v>
@@ -5739,7 +5739,7 @@
         <v>93.3</v>
       </c>
       <c r="O26">
-        <v>53.3</v>
+        <v>76.7</v>
       </c>
       <c r="P26">
         <v>71.90000000000001</v>
@@ -5766,7 +5766,7 @@
         <v>93.3</v>
       </c>
       <c r="X26">
-        <v>53.3</v>
+        <v>76.7</v>
       </c>
       <c r="Y26">
         <v>71.90000000000001</v>
@@ -5911,7 +5911,7 @@
         <v>98.3</v>
       </c>
       <c r="O28">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="P28">
         <v>90.59999999999999</v>
@@ -5938,7 +5938,7 @@
         <v>98.3</v>
       </c>
       <c r="X28">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="Y28">
         <v>90.59999999999999</v>
@@ -6141,19 +6141,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/2AEM - Estadisticos 20232.xlsx
+++ b/grupos/2AEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="110">
   <si>
     <t>Materia</t>
   </si>
@@ -182,21 +182,21 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Flores Paz Victor</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Flores Paz Victor</t>
-  </si>
-  <si>
     <t>Hernández Castro Enrique</t>
   </si>
   <si>
@@ -212,94 +212,142 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MONTERD</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>TELLO</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BERULES</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BERULES</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ATLAHUA</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>ATLAHUA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>VENTURA</t>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>OMAR DAVID</t>
+  </si>
+  <si>
+    <t>RAFAEL FELIPE</t>
+  </si>
+  <si>
+    <t>ANGEL YAMIL</t>
+  </si>
+  <si>
+    <t>LUIS DAVID</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>ERICK ANGEL</t>
+  </si>
+  <si>
+    <t>VICENTE ABIMAEL</t>
+  </si>
+  <si>
+    <t>DANA INGRID</t>
   </si>
   <si>
     <t>JUAN SEBASTIAN</t>
   </si>
   <si>
+    <t>JAIME</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
+  </si>
+  <si>
+    <t>FELIX</t>
+  </si>
+  <si>
+    <t>DANILO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JOSUE YAHIR</t>
+  </si>
+  <si>
     <t>JOEL MIGUEL</t>
-  </si>
-  <si>
-    <t>ERICK ANGEL</t>
-  </si>
-  <si>
-    <t>VICENTE ABIMAEL</t>
-  </si>
-  <si>
-    <t>DANA INGRID</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>FELIX</t>
-  </si>
-  <si>
-    <t>DANILO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -891,31 +939,31 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>5</v>
@@ -924,7 +972,7 @@
         <v>5</v>
       </c>
       <c r="AE4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF4">
         <v>5</v>
@@ -936,7 +984,7 @@
         <v>5</v>
       </c>
       <c r="AI4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ4">
         <v>6</v>
@@ -1004,40 +1052,40 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD5">
         <v>8</v>
       </c>
       <c r="AE5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF5">
         <v>9</v>
@@ -1117,46 +1165,46 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC6">
         <v>7</v>
       </c>
       <c r="AD6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE6">
         <v>6</v>
       </c>
       <c r="AF6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH6">
         <v>8</v>
@@ -1230,31 +1278,31 @@
         <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC7">
         <v>9</v>
@@ -1343,52 +1391,52 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF8">
         <v>7</v>
       </c>
       <c r="AG8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ8">
         <v>8</v>
@@ -1456,49 +1504,49 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>5</v>
       </c>
       <c r="AD9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI9">
         <v>7</v>
@@ -1569,34 +1617,34 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD10">
         <v>6</v>
@@ -1605,16 +1653,16 @@
         <v>7</v>
       </c>
       <c r="AF10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG10">
         <v>7</v>
       </c>
       <c r="AH10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ10">
         <v>8</v>
@@ -1682,34 +1730,34 @@
         <v>10</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD11">
         <v>7</v>
@@ -1795,34 +1843,34 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD12">
         <v>8</v>
@@ -1831,7 +1879,7 @@
         <v>8</v>
       </c>
       <c r="AF12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>9</v>
@@ -1908,43 +1956,43 @@
         <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE13">
         <v>9</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG13">
         <v>9</v>
@@ -1956,7 +2004,7 @@
         <v>10</v>
       </c>
       <c r="AJ13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK13">
         <v>-1</v>
@@ -2021,31 +2069,31 @@
         <v>10</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>7</v>
@@ -2134,34 +2182,34 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD15">
         <v>6</v>
@@ -2176,13 +2224,13 @@
         <v>8</v>
       </c>
       <c r="AH15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI15">
         <v>8</v>
       </c>
       <c r="AJ15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK15">
         <v>-1</v>
@@ -2247,31 +2295,31 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -2280,13 +2328,13 @@
         <v>5</v>
       </c>
       <c r="AE16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF16">
         <v>5</v>
       </c>
       <c r="AG16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH16">
         <v>5</v>
@@ -2360,31 +2408,31 @@
         <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2396,19 +2444,19 @@
         <v>7</v>
       </c>
       <c r="AF17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH17">
         <v>5</v>
       </c>
       <c r="AI17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK17">
         <v>-1</v>
@@ -2473,31 +2521,31 @@
         <v>5</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>5</v>
@@ -2586,31 +2634,31 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC19">
         <v>5</v>
@@ -2619,22 +2667,22 @@
         <v>5</v>
       </c>
       <c r="AE19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF19">
         <v>8</v>
       </c>
       <c r="AG19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK19">
         <v>-1</v>
@@ -2699,52 +2747,52 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC20">
         <v>5</v>
       </c>
       <c r="AD20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG20">
         <v>6</v>
       </c>
       <c r="AH20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ20">
         <v>7</v>
@@ -2812,31 +2860,31 @@
         <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>5</v>
@@ -2845,19 +2893,19 @@
         <v>5</v>
       </c>
       <c r="AE21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG21">
         <v>5</v>
       </c>
       <c r="AH21">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ21">
         <v>8</v>
@@ -2925,55 +2973,55 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>5</v>
       </c>
       <c r="AD22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK22">
         <v>-1</v>
@@ -3038,31 +3086,31 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC23">
         <v>7</v>
@@ -3077,7 +3125,7 @@
         <v>8</v>
       </c>
       <c r="AG23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH23">
         <v>10</v>
@@ -3151,31 +3199,31 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC24">
         <v>6</v>
@@ -3190,7 +3238,7 @@
         <v>8</v>
       </c>
       <c r="AG24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH24">
         <v>9</v>
@@ -3199,7 +3247,7 @@
         <v>8</v>
       </c>
       <c r="AJ24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK24">
         <v>-1</v>
@@ -3264,52 +3312,52 @@
         <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>5</v>
       </c>
       <c r="AD25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ25">
         <v>7</v>
@@ -3377,52 +3425,52 @@
         <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ26">
         <v>8</v>
@@ -3490,40 +3538,40 @@
         <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF27">
         <v>9</v>
@@ -3538,7 +3586,7 @@
         <v>9</v>
       </c>
       <c r="AJ27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK27">
         <v>-1</v>
@@ -3603,49 +3651,49 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC28">
         <v>5</v>
       </c>
       <c r="AD28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG28">
         <v>6</v>
       </c>
       <c r="AH28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI28">
         <v>6</v>
@@ -3862,25 +3910,25 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>86.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="U4">
-        <v>82.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V4">
         <v>100</v>
       </c>
       <c r="W4">
-        <v>31.7</v>
+        <v>37.5</v>
       </c>
       <c r="X4">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="Y4">
-        <v>46.9</v>
+        <v>39.6</v>
       </c>
       <c r="Z4">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AA4">
         <v>100</v>
@@ -3948,7 +3996,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -3963,10 +4011,10 @@
         <v>100</v>
       </c>
       <c r="Y5">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z5">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA5">
         <v>100</v>
@@ -4034,7 +4082,7 @@
         <v>100</v>
       </c>
       <c r="T6">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U6">
         <v>100</v>
@@ -4043,16 +4091,16 @@
         <v>100</v>
       </c>
       <c r="W6">
-        <v>98.3</v>
+        <v>94.8</v>
       </c>
       <c r="X6">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="Y6">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z6">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA6">
         <v>100</v>
@@ -4135,10 +4183,10 @@
         <v>100</v>
       </c>
       <c r="Y7">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z7">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AA7">
         <v>100</v>
@@ -4206,25 +4254,25 @@
         <v>100</v>
       </c>
       <c r="T8">
-        <v>95.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U8">
-        <v>95.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="V8">
         <v>100</v>
       </c>
       <c r="W8">
-        <v>95</v>
+        <v>91.7</v>
       </c>
       <c r="X8">
-        <v>73.3</v>
+        <v>83.3</v>
       </c>
       <c r="Y8">
-        <v>65.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="Z8">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AA8">
         <v>100</v>
@@ -4292,28 +4340,28 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>63.6</v>
+        <v>59.4</v>
       </c>
       <c r="U9">
-        <v>95.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="V9">
         <v>100</v>
       </c>
       <c r="W9">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X9">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="Y9">
-        <v>78.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="Z9">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA9">
-        <v>91</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AB9">
         <v>100</v>
@@ -4378,25 +4426,25 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>77.3</v>
+        <v>81.3</v>
       </c>
       <c r="U10">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V10">
         <v>100</v>
       </c>
       <c r="W10">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
       <c r="X10">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="Y10">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Z10">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA10">
         <v>100</v>
@@ -4464,7 +4512,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -4473,7 +4521,7 @@
         <v>100</v>
       </c>
       <c r="W11">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X11">
         <v>100</v>
@@ -4482,7 +4530,7 @@
         <v>100</v>
       </c>
       <c r="Z11">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA11">
         <v>100</v>
@@ -4550,7 +4598,7 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -4559,16 +4607,16 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>98.3</v>
+        <v>95.8</v>
       </c>
       <c r="X12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Y12">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z12">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA12">
         <v>100</v>
@@ -4636,25 +4684,25 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U13">
-        <v>95.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="V13">
         <v>100</v>
       </c>
       <c r="W13">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="X13">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y13">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z13">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA13">
         <v>100</v>
@@ -4722,25 +4770,25 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="U14">
-        <v>95.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X14">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y14">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z14">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA14">
         <v>100</v>
@@ -4808,25 +4856,25 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U15">
-        <v>95.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="W15">
-        <v>88.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X15">
         <v>100</v>
       </c>
       <c r="Y15">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z15">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA15">
         <v>100</v>
@@ -4894,22 +4942,22 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>77.3</v>
+        <v>53.1</v>
       </c>
       <c r="U16">
-        <v>92.7</v>
+        <v>95.2</v>
       </c>
       <c r="V16">
         <v>100</v>
       </c>
       <c r="W16">
-        <v>28.3</v>
+        <v>41.7</v>
       </c>
       <c r="X16">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="Y16">
-        <v>56.3</v>
+        <v>43.8</v>
       </c>
       <c r="Z16">
         <v>100</v>
@@ -4980,25 +5028,25 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>72.7</v>
+        <v>75</v>
       </c>
       <c r="U17">
-        <v>82.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V17">
         <v>100</v>
       </c>
       <c r="W17">
-        <v>91.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="X17">
-        <v>86.7</v>
+        <v>87.5</v>
       </c>
       <c r="Y17">
-        <v>75</v>
+        <v>79.2</v>
       </c>
       <c r="Z17">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AA17">
         <v>100</v>
@@ -5066,31 +5114,31 @@
         <v>48.6</v>
       </c>
       <c r="T18">
-        <v>31.8</v>
+        <v>21.9</v>
       </c>
       <c r="U18">
-        <v>39</v>
+        <v>25.4</v>
       </c>
       <c r="V18">
         <v>100</v>
       </c>
       <c r="W18">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="X18">
-        <v>33.3</v>
+        <v>20.8</v>
       </c>
       <c r="Y18">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="Z18">
-        <v>74</v>
+        <v>52.9</v>
       </c>
       <c r="AA18">
-        <v>43.8</v>
+        <v>34.2</v>
       </c>
       <c r="AB18">
-        <v>48.6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:28">
@@ -5152,28 +5200,28 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>77.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="U19">
-        <v>95.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="V19">
         <v>100</v>
       </c>
       <c r="W19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X19">
-        <v>96.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Y19">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Z19">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AA19">
-        <v>97.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AB19">
         <v>100</v>
@@ -5238,28 +5286,28 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U20">
-        <v>82.90000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="V20">
         <v>100</v>
       </c>
       <c r="W20">
-        <v>93.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X20">
-        <v>96.7</v>
+        <v>95.8</v>
       </c>
       <c r="Y20">
+        <v>91.7</v>
+      </c>
+      <c r="Z20">
+        <v>90</v>
+      </c>
+      <c r="AA20">
         <v>87.5</v>
-      </c>
-      <c r="Z20">
-        <v>86</v>
-      </c>
-      <c r="AA20">
-        <v>84</v>
       </c>
       <c r="AB20">
         <v>100</v>
@@ -5324,28 +5372,28 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="U21">
-        <v>92.7</v>
+        <v>95.2</v>
       </c>
       <c r="V21">
         <v>100</v>
       </c>
       <c r="W21">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="X21">
-        <v>70</v>
+        <v>70.8</v>
       </c>
       <c r="Y21">
-        <v>71.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="Z21">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AA21">
-        <v>97.90000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AB21">
         <v>100</v>
@@ -5410,7 +5458,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -5419,19 +5467,19 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>95</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X22">
-        <v>93.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Y22">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Z22">
-        <v>84</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="AA22">
-        <v>89.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="AB22">
         <v>100</v>
@@ -5505,16 +5553,16 @@
         <v>100</v>
       </c>
       <c r="W23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X23">
         <v>100</v>
       </c>
       <c r="Y23">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z23">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA23">
         <v>100</v>
@@ -5582,7 +5630,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -5591,16 +5639,16 @@
         <v>100</v>
       </c>
       <c r="W24">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="X24">
         <v>100</v>
       </c>
       <c r="Y24">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Z24">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA24">
         <v>100</v>
@@ -5668,25 +5716,25 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>77.3</v>
+        <v>75</v>
       </c>
       <c r="U25">
-        <v>92.7</v>
+        <v>95.2</v>
       </c>
       <c r="V25">
         <v>100</v>
       </c>
       <c r="W25">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="X25">
+        <v>95.8</v>
+      </c>
+      <c r="Y25">
         <v>91.7</v>
       </c>
-      <c r="X25">
-        <v>100</v>
-      </c>
-      <c r="Y25">
-        <v>87.5</v>
-      </c>
       <c r="Z25">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AA25">
         <v>100</v>
@@ -5700,7 +5748,7 @@
         <v>37</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C26">
         <v>89.5</v>
@@ -5727,7 +5775,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>36.4</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L26">
         <v>95.09999999999999</v>
@@ -5754,25 +5802,25 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>36.4</v>
+        <v>93.8</v>
       </c>
       <c r="U26">
-        <v>95.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="V26">
         <v>100</v>
       </c>
       <c r="W26">
-        <v>93.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X26">
-        <v>76.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Y26">
-        <v>71.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="Z26">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AA26">
         <v>100</v>
@@ -5840,10 +5888,10 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U27">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V27">
         <v>100</v>
@@ -5855,10 +5903,10 @@
         <v>100</v>
       </c>
       <c r="Y27">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Z27">
-        <v>88</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="AA27">
         <v>100</v>
@@ -5926,25 +5974,25 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U28">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="V28">
         <v>100</v>
       </c>
       <c r="W28">
-        <v>98.3</v>
+        <v>95.8</v>
       </c>
       <c r="X28">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="Y28">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Z28">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AA28">
         <v>100</v>
@@ -6045,16 +6093,16 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="G3" s="2">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="H3">
         <v>6.1</v>
@@ -6068,7 +6116,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -6077,19 +6125,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="G4" s="2">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6100,7 +6148,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -6109,19 +6157,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="G5" s="2">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6132,7 +6180,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -6141,19 +6189,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="G6" s="2">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6164,7 +6212,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -6173,19 +6221,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="G7" s="2">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6196,7 +6244,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>58</v>
@@ -6205,19 +6253,19 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="G8" s="2">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6237,19 +6285,19 @@
         <v>25</v>
       </c>
       <c r="D9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G9" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6281,7 +6329,7 @@
         <v>4</v>
       </c>
       <c r="H10">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -6331,7 +6379,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6363,22 +6411,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920008</v>
+        <v>23330051920005</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6386,16 +6434,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920008</v>
+        <v>23330051920005</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -6409,16 +6457,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920024</v>
+        <v>23330051920006</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -6432,16 +6480,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920024</v>
+        <v>23330051920006</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -6455,39 +6503,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920003</v>
+        <v>23330051920017</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920002</v>
+        <v>23330051920017</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -6501,39 +6549,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920004</v>
+        <v>23330051920321</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920009</v>
+        <v>23330051920321</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -6547,39 +6595,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920026</v>
+        <v>23330051920022</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920010</v>
+        <v>23330051920022</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -6593,16 +6641,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920012</v>
+        <v>23330051920003</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
@@ -6616,16 +6664,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920013</v>
+        <v>23330051920002</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
@@ -6639,16 +6687,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920021</v>
+        <v>23330051920004</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
         <v>13</v>
@@ -6662,16 +6710,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920020</v>
+        <v>23330051920008</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
@@ -6680,6 +6728,213 @@
         <v>52</v>
       </c>
       <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920009</v>
+      </c>
+      <c r="B16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920026</v>
+      </c>
+      <c r="B17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920010</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920012</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920013</v>
+      </c>
+      <c r="B20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920021</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920020</v>
+      </c>
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920023</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920024</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2AEM - Estadisticos 20232.xlsx
+++ b/grupos/2AEM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="85">
   <si>
     <t>Materia</t>
   </si>
@@ -176,30 +176,30 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Flores Paz Victor</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Hernández Castro Enrique</t>
+  </si>
+  <si>
     <t>Cruz Alejo José Armando</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
-    <t>Flores Paz Victor</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Hernández Castro Enrique</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -212,6 +212,12 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
@@ -227,48 +233,18 @@
     <t>TELLO</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BERULES</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
   </si>
   <si>
     <t>VASQUEZ</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>VENTURA</t>
   </si>
   <si>
@@ -278,25 +254,10 @@
     <t>DE LA LUZ</t>
   </si>
   <si>
-    <t>ATLAHUA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
+    <t>HERSON</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
   </si>
   <si>
     <t>OMAR DAVID</t>
@@ -312,42 +273,6 @@
   </si>
   <si>
     <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>ERICK ANGEL</t>
-  </si>
-  <si>
-    <t>VICENTE ABIMAEL</t>
-  </si>
-  <si>
-    <t>DANA INGRID</t>
-  </si>
-  <si>
-    <t>JUAN SEBASTIAN</t>
-  </si>
-  <si>
-    <t>JAIME</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>FELIX</t>
-  </si>
-  <si>
-    <t>DANILO</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JOSUE YAHIR</t>
-  </si>
-  <si>
-    <t>JOEL MIGUEL</t>
   </si>
 </sst>
 </file>
@@ -990,7 +915,7 @@
         <v>6</v>
       </c>
       <c r="AK4">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1103,7 +1028,7 @@
         <v>9</v>
       </c>
       <c r="AK5">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1216,7 +1141,7 @@
         <v>8</v>
       </c>
       <c r="AK6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1329,7 +1254,7 @@
         <v>9</v>
       </c>
       <c r="AK7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1442,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="AK8">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1555,7 +1480,7 @@
         <v>7</v>
       </c>
       <c r="AK9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1668,7 +1593,7 @@
         <v>8</v>
       </c>
       <c r="AK10">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1781,7 +1706,7 @@
         <v>9</v>
       </c>
       <c r="AK11">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1894,7 +1819,7 @@
         <v>9</v>
       </c>
       <c r="AK12">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2007,7 +1932,7 @@
         <v>8</v>
       </c>
       <c r="AK13">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2120,7 +2045,7 @@
         <v>10</v>
       </c>
       <c r="AK14">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2233,7 +2158,7 @@
         <v>7</v>
       </c>
       <c r="AK15">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2346,7 +2271,7 @@
         <v>8</v>
       </c>
       <c r="AK16">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2459,7 +2384,7 @@
         <v>7</v>
       </c>
       <c r="AK17">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2572,7 +2497,7 @@
         <v>5</v>
       </c>
       <c r="AK18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2685,7 +2610,7 @@
         <v>8</v>
       </c>
       <c r="AK19">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2798,7 +2723,7 @@
         <v>7</v>
       </c>
       <c r="AK20">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -2911,7 +2836,7 @@
         <v>8</v>
       </c>
       <c r="AK21">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -3024,7 +2949,7 @@
         <v>7</v>
       </c>
       <c r="AK22">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3137,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="AK23">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3250,7 +3175,7 @@
         <v>8</v>
       </c>
       <c r="AK24">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3363,7 +3288,7 @@
         <v>7</v>
       </c>
       <c r="AK25">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3476,7 +3401,7 @@
         <v>8</v>
       </c>
       <c r="AK26">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -3589,7 +3514,7 @@
         <v>8</v>
       </c>
       <c r="AK27">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -3702,7 +3627,7 @@
         <v>7</v>
       </c>
       <c r="AK28">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -6055,7 +5980,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>52</v>
@@ -6064,27 +5989,30 @@
         <v>25</v>
       </c>
       <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2">
+        <v>56</v>
+      </c>
+      <c r="G2" s="2">
+        <v>44</v>
+      </c>
+      <c r="H2">
+        <v>6.1</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>25</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -6093,19 +6021,19 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="G3" s="2">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6116,7 +6044,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
@@ -6125,19 +6053,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G4" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6148,7 +6076,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -6157,19 +6085,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G5" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6180,7 +6108,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -6201,7 +6129,7 @@
         <v>12</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6212,7 +6140,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -6221,19 +6149,19 @@
         <v>25</v>
       </c>
       <c r="D7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G7" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6244,7 +6172,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>58</v>
@@ -6265,7 +6193,7 @@
         <v>4</v>
       </c>
       <c r="H8">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6276,7 +6204,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>59</v>
@@ -6297,7 +6225,7 @@
         <v>4</v>
       </c>
       <c r="H9">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6308,10 +6236,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>25</v>
@@ -6329,7 +6257,7 @@
         <v>4</v>
       </c>
       <c r="H10">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -6379,7 +6307,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6411,22 +6339,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920005</v>
+        <v>23330051920016</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6434,45 +6362,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920005</v>
+        <v>23330051920016</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920006</v>
+        <v>23330051920025</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6480,45 +6408,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920006</v>
+        <v>23330051920025</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920017</v>
+        <v>23330051920005</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6526,45 +6454,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920017</v>
+        <v>23330051920006</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>52</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920321</v>
+        <v>23330051920017</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6575,22 +6503,22 @@
         <v>23330051920321</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>52</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -6598,344 +6526,22 @@
         <v>23330051920022</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G10">
         <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920022</v>
-      </c>
-      <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920003</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>75</v>
-      </c>
-      <c r="D12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920002</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E13" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920004</v>
-      </c>
-      <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920008</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920009</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920026</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920010</v>
-      </c>
-      <c r="B18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920012</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920013</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>90</v>
-      </c>
-      <c r="D20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920021</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" t="s">
-        <v>103</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920020</v>
-      </c>
-      <c r="B22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920023</v>
-      </c>
-      <c r="B23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>108</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920024</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" t="s">
-        <v>109</v>
-      </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>
